--- a/reports/devops-jobs-israel-2026-W33.xlsx
+++ b/reports/devops-jobs-israel-2026-W33.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-10T07:57:44</t>
+    <t xml:space="preserve">2026-08-11T07:20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-12</t>
+    <t xml:space="preserve">2026-08-11</t>
   </si>
   <si>
     <t xml:space="preserve">Devops Student</t>
@@ -402,15 +402,6 @@
     <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
-    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Devops Engineer</t>
   </si>
   <si>
@@ -420,819 +411,801 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
+    <t xml:space="preserve">Scytale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4448083785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4449509251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4449541386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Jerusalem</t>
   </si>
   <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4451527258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid-Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArtAc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid-senior-devops-engineer-at-artac-4449647364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Agentic Search)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-agentic-search-at-nebius-4449552344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Engineer (Chaos DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/chaos-engineer-chaos-devops-at-check-point-software-4449688636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-artac-4449652341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGO NEXT Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4449550588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4449812270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4449562024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Scytale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead (37248)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451509573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4451528239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (Hands-on)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sigal Dori (Tepper)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-hands-on-at-sigal-dori-tepper-4448430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4448083785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4446200013</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4450940462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha | Similarweb Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-alpha-similarweb-partner-4447362032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-voyantis-4448003083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solutions / Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APERIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/solutions-site-reliability-engineer-at-aperio-4451514889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4448004083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4449299724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alictus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-alictus-4450008323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4451564107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com AI engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-ai-engineering-4449050085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer / Technical Lead (AWS &amp; GCP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-technical-lead-aws-gcp-at-anyclip-4446636401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4449655270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4447388666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLVTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-tlvtech-4449569052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Client Oriented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-client-oriented-at-kpmg-israel-4451134408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4451336717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4448093647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Architect (37188)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-37188-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451517385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4447391644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4447375577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-03</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4449509251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4449541386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid-Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ArtAc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid-senior-devops-engineer-at-artac-4449647364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaos Engineer (Chaos DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/chaos-engineer-chaos-devops-at-check-point-software-4449688636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4441121726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-artac-4449652341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGO NEXT Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridgify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bridgify-4441525178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pagaya-4316888825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (Hands-on)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sigal Dori (Tepper)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-hands-on-at-sigal-dori-tepper-4448430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4450940462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש.אשת DevOps Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dahan Lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-devops-linux-at-dahan-lab-4449061474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha | Similarweb Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-alpha-similarweb-partner-4447362032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-voyantis-4448003083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4450225101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4449299724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team leader, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zadara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team-leader-devops-at-zadara-4448858731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4447391644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4448004083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Technical Lead, DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-technical-lead-devops-group-at-bigpanda-4447980511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alictus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-alictus-4450008323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com AI engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-ai-engineering-4449050085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer / Technical Lead (AWS &amp; GCP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-technical-lead-aws-gcp-at-anyclip-4446636401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4449655270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4448323071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4447388666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4451336717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4448093647</t>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
   </si>
   <si>
     <t xml:space="preserve">System Engineer 24246</t>
   </si>
   <si>
-    <t xml:space="preserve">comblack</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-24246-at-comblack-4450246628</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDO Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-bdo-israel-4450913545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4447375577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Storage &amp; Backup Infrastructure Engineer (5489)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-storage-backup-infrastructure-engineer-5489-at-ingima-4451343138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1341,6 +1314,18 @@
     <t xml:space="preserve">2026-07-01</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unilink Ltd.</t>
   </si>
   <si>
@@ -1353,27 +1338,9 @@
     <t xml:space="preserve">2026-07-31</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
     <t xml:space="preserve">L3 Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1389,10 +1356,10 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
@@ -1556,7 +1523,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -1564,7 +1531,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -1572,7 +1539,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -1580,7 +1547,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1216</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1627,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1679,28 +1646,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1708,7 +1675,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1727,119 +1694,119 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>239</v>
+        <v>347</v>
       </c>
       <c r="B4" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="B5" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B6" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>457</v>
+        <v>345</v>
       </c>
       <c r="B7" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B8" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>357</v>
+        <v>447</v>
       </c>
       <c r="B9" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="B10" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>460</v>
+        <v>341</v>
       </c>
       <c r="B11" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B12" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>354</v>
+        <v>449</v>
       </c>
       <c r="B13" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="B15" s="3">
         <v>9</v>
@@ -1847,10 +1814,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1875,13 +1842,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2">
@@ -1889,13 +1856,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3">
-        <v>12.2</v>
+        <v>13.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1904,88 +1871,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3">
-        <v>34.8</v>
+        <v>33.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.6</v>
+        <v>2.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.8</v>
+        <v>33.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.5</v>
+        <v>15.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.6</v>
+        <v>16.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1998,7 +1965,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2069,7 +2036,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2101,7 +2068,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -2133,7 +2100,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
@@ -2165,7 +2132,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2197,7 +2164,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2229,7 +2196,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2261,7 +2228,7 @@
         <v>67</v>
       </c>
       <c r="J8" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
@@ -2293,7 +2260,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -2325,7 +2292,7 @@
         <v>67</v>
       </c>
       <c r="J10" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -2357,7 +2324,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
@@ -2389,7 +2356,7 @@
         <v>85</v>
       </c>
       <c r="J12" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -2421,7 +2388,7 @@
         <v>46</v>
       </c>
       <c r="J13" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -2453,7 +2420,7 @@
         <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
@@ -2485,7 +2452,7 @@
         <v>71</v>
       </c>
       <c r="J15" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -2517,7 +2484,7 @@
         <v>99</v>
       </c>
       <c r="J16" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
@@ -2549,7 +2516,7 @@
         <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -2581,7 +2548,7 @@
         <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2613,7 +2580,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
@@ -2645,7 +2612,7 @@
         <v>120</v>
       </c>
       <c r="J20" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2677,7 +2644,7 @@
         <v>126</v>
       </c>
       <c r="J21" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22">
@@ -2694,57 +2661,57 @@
         <v>49</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>131</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>132</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="J23" s="3">
-        <v>90</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>134</v>
@@ -2753,14 +2720,14 @@
         <v>135</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>136</v>
@@ -2769,7 +2736,7 @@
         <v>137</v>
       </c>
       <c r="J24" s="3">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
@@ -2783,7 +2750,7 @@
         <v>139</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>43</v>
@@ -2796,15 +2763,15 @@
         <v>140</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="J25" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>142</v>
@@ -2813,7 +2780,7 @@
         <v>143</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>43</v>
@@ -2826,10 +2793,10 @@
         <v>144</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="J26" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27">
@@ -2837,10 +2804,10 @@
         <v>106</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>49</v>
@@ -2853,24 +2820,24 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J27" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>49</v>
@@ -2883,24 +2850,24 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="J28" s="3">
-        <v>4</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>153</v>
+        <v>106</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>112</v>
@@ -2913,13 +2880,13 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J29" s="3">
-        <v>87</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2927,10 +2894,10 @@
         <v>106</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>49</v>
@@ -2943,24 +2910,24 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J30" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>112</v>
@@ -2973,27 +2940,27 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -3003,13 +2970,13 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="J32" s="3">
-        <v>85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -3017,13 +2984,13 @@
         <v>106</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -3033,10 +3000,10 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>159</v>
+        <v>41</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -3044,19 +3011,19 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
@@ -3069,21 +3036,21 @@
         <v>171</v>
       </c>
       <c r="J34" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>106</v>
+        <v>172</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>43</v>
@@ -3096,27 +3063,27 @@
         <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
@@ -3126,24 +3093,24 @@
         <v>178</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>179</v>
+        <v>41</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>43</v>
@@ -3159,21 +3126,21 @@
         <v>183</v>
       </c>
       <c r="J37" s="3">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>186</v>
+        <v>49</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>43</v>
@@ -3183,209 +3150,209 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>188</v>
+        <v>133</v>
       </c>
       <c r="J38" s="3">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="J39" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>53</v>
+        <v>188</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="J41" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="D42" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J42" s="3">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>202</v>
+        <v>53</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>203</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>205</v>
+        <v>41</v>
       </c>
       <c r="J43" s="3">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>206</v>
+        <v>53</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="J44" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>43</v>
@@ -3395,87 +3362,87 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="J45" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="J46" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>217</v>
+        <v>135</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
       <c r="J47" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>220</v>
+        <v>106</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>186</v>
+        <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>43</v>
@@ -3485,43 +3452,43 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="J48" s="3">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>53</v>
+        <v>214</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="J49" s="3">
-        <v>3</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50">
@@ -3529,10 +3496,10 @@
         <v>53</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
@@ -3545,27 +3512,27 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>226</v>
+        <v>171</v>
       </c>
       <c r="J50" s="3">
-        <v>47</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>38</v>
@@ -3575,13 +3542,13 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="J51" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3589,10 +3556,10 @@
         <v>53</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3605,27 +3572,27 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="J52" s="3">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>151</v>
+        <v>227</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>49</v>
+        <v>228</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>38</v>
@@ -3635,24 +3602,24 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>179</v>
+        <v>41</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
@@ -3665,86 +3632,84 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>239</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>241</v>
+        <v>147</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>53</v>
+        <v>237</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>143</v>
+        <v>235</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>241</v>
+        <v>199</v>
       </c>
       <c r="J56" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
@@ -3757,54 +3722,54 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>247</v>
+        <v>53</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J58" s="3">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>53</v>
+        <v>246</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>49</v>
@@ -3817,10 +3782,10 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>241</v>
+        <v>133</v>
       </c>
       <c r="J59" s="3">
         <v>5</v>
@@ -3828,32 +3793,32 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>53</v>
+        <v>249</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>147</v>
+        <v>235</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>141</v>
+        <v>252</v>
       </c>
       <c r="J60" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
@@ -3861,13 +3826,13 @@
         <v>53</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>256</v>
+        <v>135</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>257</v>
+        <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3877,57 +3842,57 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>43</v>
@@ -3937,40 +3902,40 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="J63" s="3">
-        <v>4</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>159</v>
+        <v>41</v>
       </c>
       <c r="J64" s="3">
         <v>0</v>
@@ -3978,16 +3943,16 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>38</v>
@@ -3997,27 +3962,27 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="J65" s="3">
-        <v>87</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>143</v>
+        <v>269</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>43</v>
@@ -4027,24 +3992,24 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J66" s="3">
-        <v>87</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>177</v>
+        <v>272</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>112</v>
@@ -4057,86 +4022,84 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="J67" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>277</v>
+        <v>53</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>264</v>
+        <v>227</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="J68" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="J69" s="3">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>283</v>
+        <v>56</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
@@ -4149,179 +4112,179 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>120</v>
+        <v>282</v>
       </c>
       <c r="J70" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>149</v>
+        <v>41</v>
       </c>
       <c r="J71" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>56</v>
+        <v>286</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>211</v>
+        <v>135</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J73" s="3">
-        <v>67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>143</v>
+        <v>293</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>294</v>
+      </c>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="I75" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="J75" s="3">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>139</v>
+        <v>235</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>43</v>
@@ -4331,57 +4294,57 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="J76" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>306</v>
+        <v>168</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>308</v>
+        <v>133</v>
       </c>
       <c r="J77" s="3">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>147</v>
+        <v>306</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>43</v>
@@ -4391,10 +4354,10 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>241</v>
+        <v>133</v>
       </c>
       <c r="J78" s="3">
         <v>5</v>
@@ -4402,46 +4365,46 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>176</v>
+        <v>309</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="J79" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>316</v>
+        <v>131</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>43</v>
@@ -4451,57 +4414,59 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="J80" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>263</v>
+        <v>315</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>319</v>
+        <v>135</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>186</v>
+        <v>49</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="J81" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>321</v>
+        <v>34</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>324</v>
+        <v>112</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>38</v>
@@ -4511,148 +4476,150 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="J83" s="3">
-        <v>3</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>330</v>
+        <v>135</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F84" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>203</v>
+        <v>328</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="J85" s="3">
-        <v>87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>336</v>
+        <v>220</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>203</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>179</v>
+        <v>41</v>
       </c>
       <c r="J86" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>339</v>
+        <v>268</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>139</v>
+        <v>269</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>112</v>
@@ -4665,24 +4632,24 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>139</v>
+        <v>336</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>112</v>
@@ -4695,77 +4662,17 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="J89" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J90" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J90"/>
+  <autoFilter ref="A1:J88"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4854,8 +4761,6 @@
     <hyperlink ref="H86" r:id="rId85"/>
     <hyperlink ref="H87" r:id="rId86"/>
     <hyperlink ref="H88" r:id="rId87"/>
-    <hyperlink ref="H89" r:id="rId88"/>
-    <hyperlink ref="H90" r:id="rId89"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4863,9 +4768,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4897,127 +4802,127 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>157</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>167</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>168</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>172</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>173</v>
+        <v>49</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>174</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>197</v>
+        <v>58</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>235</v>
+        <v>59</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>236</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>256</v>
+        <v>49</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>258</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>266</v>
+        <v>127</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>192</v>
+        <v>122</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>193</v>
+        <v>123</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>267</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>321</v>
+        <v>157</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>322</v>
+        <v>158</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>323</v>
+        <v>143</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5025,18 +4930,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>325</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>329</v>
+        <v>163</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>330</v>
+        <v>164</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5044,18 +4949,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>331</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>341</v>
+        <v>176</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>342</v>
+        <v>177</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5063,15 +4968,15 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>343</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>348</v>
+        <v>53</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>349</v>
+        <v>200</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>139</v>
@@ -5082,11 +4987,239 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>350</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G23"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5098,6 +5231,18 @@
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
+    <hyperlink ref="G23" r:id="rId22"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5111,15 +5256,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="B2" s="3">
         <v>15</v>
@@ -5127,7 +5272,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="B3" s="3">
         <v>15</v>
@@ -5135,23 +5280,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="B4" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="B5" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="B6" s="3">
         <v>11</v>
@@ -5159,15 +5304,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>239</v>
+        <v>344</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
@@ -5175,7 +5320,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -5183,7 +5328,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5191,7 +5336,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -5199,7 +5344,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B12" s="3">
         <v>6</v>
@@ -5207,7 +5352,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -5215,7 +5360,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5223,7 +5368,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5231,7 +5376,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5244,7 +5389,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5253,7 +5398,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2">
@@ -5282,7 +5427,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5290,7 +5435,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>176</v>
+        <v>268</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5298,15 +5443,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>263</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5314,7 +5459,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5322,7 +5467,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5330,7 +5475,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5338,7 +5483,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5346,23 +5491,23 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>101</v>
+        <v>220</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5370,7 +5515,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5384,23 +5529,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2">
@@ -5436,10 +5581,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="C4" s="3">
-        <v>8.8</v>
+        <v>7.2</v>
       </c>
       <c r="D4" s="3">
         <v>3</v>
@@ -5450,13 +5595,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5464,10 +5609,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="C6" s="3">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5478,10 +5623,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="C7" s="3">
-        <v>5.3</v>
+        <v>5.0</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5492,7 +5637,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C8" s="3">
         <v>4.2</v>
@@ -5506,7 +5651,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
@@ -5534,13 +5679,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="C11" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5548,13 +5693,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="C12" s="3">
         <v>2.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5562,10 +5707,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="C13" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -5576,7 +5721,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5590,13 +5735,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="C15" s="3">
-        <v>2.0</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -5604,13 +5749,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>101</v>
+        <v>220</v>
       </c>
       <c r="C16" s="3">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5630,10 +5775,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2">
@@ -5652,10 +5797,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4">
@@ -5663,10 +5808,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -5685,7 +5830,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
@@ -5701,20 +5846,20 @@
         <v>112</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>181</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5722,10 +5867,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>228</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -5738,17 +5883,9 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>257</v>
+        <v>165</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5773,10 +5910,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5788,10 +5925,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5808,31 +5945,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3">
@@ -5840,31 +5977,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4">
@@ -5872,31 +6009,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>162</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5">
@@ -5904,31 +6041,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6">
@@ -5936,28 +6073,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>392</v>
+        <v>283</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>115</v>
@@ -5977,13 +6114,13 @@
         <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="F7" s="3">
         <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>24</v>
@@ -6000,31 +6137,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="F8" s="3">
         <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>162</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -6032,31 +6169,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>338</v>
+        <v>392</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>339</v>
+        <v>284</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F9" s="3">
         <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
@@ -6064,31 +6201,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F10" s="3">
         <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -6105,13 +6242,13 @@
         <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="F11" s="3">
         <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>24</v>
@@ -6128,28 +6265,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F12" s="3">
         <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>85</v>
@@ -6160,31 +6297,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F13" s="3">
         <v>76</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14">
@@ -6192,7 +6329,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>35</v>
@@ -6201,22 +6338,22 @@
         <v>36</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F14" s="3">
         <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15">
@@ -6224,31 +6361,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F15" s="3">
         <v>56</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16">
@@ -6256,31 +6393,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>193</v>
+        <v>272</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F16" s="3">
         <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17">
@@ -6288,31 +6425,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F17" s="3">
         <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18">
@@ -6320,31 +6457,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="F18" s="3">
         <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19">
@@ -6352,31 +6489,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>344</v>
+        <v>431</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>151</v>
+        <v>235</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F19" s="3">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>443</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -6384,31 +6521,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>444</v>
+        <v>334</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21">
@@ -6416,31 +6553,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>450</v>
+        <v>177</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="F21" s="3">
         <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W33.xlsx
+++ b/reports/devops-jobs-israel-2026-W33.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="450">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-11T07:20:54</t>
+    <t xml:space="preserve">2026-08-12T07:44:20</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4%</t>
+    <t xml:space="preserve">3.5%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -339,6 +339,18 @@
     <t xml:space="preserve">2026-07-05</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
@@ -435,6 +447,12 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
     <t xml:space="preserve">Buildots</t>
   </si>
   <si>
@@ -444,840 +462,768 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4448083785</t>
   </si>
   <si>
+    <t xml:space="preserve">Agora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4449509251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4449541386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4451527258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid-Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArtAc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid-senior-devops-engineer-at-artac-4449647364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Agentic Search)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-agentic-search-at-nebius-4449552344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Engineer (Chaos DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/chaos-engineer-chaos-devops-at-check-point-software-4449688636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-artac-4449652341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLVTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-tlvtech-4449569052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4449841507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4449299724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4450225101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead (37248)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451509573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4451528239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4450940462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-voyantis-4448003083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solutions / Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APERIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/solutions-site-reliability-engineer-at-aperio-4451514889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4448004083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alictus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-alictus-4450008323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-nimble-4452451963</t>
+  </si>
+  <si>
     <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
   </si>
   <si>
+    <t xml:space="preserve">ERGO NEXT Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4451564107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-atera-4449731971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451456954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4449812270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4447388666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4449562024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Client Oriented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-client-oriented-at-kpmg-israel-4451134408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4451336717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4449655270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4449550588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4447375577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4447391644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thales</t>
   </si>
   <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4449509251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4449541386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4451527258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid-Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ArtAc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid-senior-devops-engineer-at-artac-4449647364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Agentic Search)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-agentic-search-at-nebius-4449552344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaos Engineer (Chaos DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/chaos-engineer-chaos-devops-at-check-point-software-4449688636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-artac-4449652341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-15</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGO NEXT Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4449550588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4449812270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4449562024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead (37248)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451509573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4452408106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4451528239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (Hands-on)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sigal Dori (Tepper)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-hands-on-at-sigal-dori-tepper-4448430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4450940462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha | Similarweb Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-alpha-similarweb-partner-4447362032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-voyantis-4448003083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solutions / Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APERIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/solutions-site-reliability-engineer-at-aperio-4451514889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4448004083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4449299724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alictus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-alictus-4450008323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4451564107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com AI engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-ai-engineering-4449050085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer / Technical Lead (AWS &amp; GCP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-technical-lead-aws-gcp-at-anyclip-4446636401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4449655270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4447388666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLVTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-tlvtech-4449569052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Client Oriented</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-client-oriented-at-kpmg-israel-4451134408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4451336717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4448093647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Architect (37188)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-37188-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451517385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4447391644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4447375577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer 24246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-24246-at-comblack-4450246628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator &amp; IT</t>
   </si>
   <si>
@@ -1338,13 +1284,37 @@
     <t xml:space="preserve">2026-07-31</t>
   </si>
   <si>
-    <t xml:space="preserve">L3 Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
+    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGILINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1356,10 +1326,10 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
@@ -1523,7 +1493,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -1531,7 +1501,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1539,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1547,7 +1517,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1238</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="10">
@@ -1619,7 +1589,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -1627,7 +1597,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1646,20 +1616,20 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -1667,7 +1637,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1675,7 +1645,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1694,119 +1664,119 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B4" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="B6" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>345</v>
+        <v>436</v>
       </c>
       <c r="B7" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>447</v>
+        <v>337</v>
       </c>
       <c r="B9" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="B10" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>341</v>
+        <v>439</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>449</v>
+        <v>333</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B15" s="3">
         <v>9</v>
@@ -1814,10 +1784,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1842,13 +1812,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2">
@@ -1856,13 +1826,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3">
-        <v>13.8</v>
+        <v>12.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1871,19 +1841,19 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3">
-        <v>33.7</v>
+        <v>38.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -1892,67 +1862,67 @@
         <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.7</v>
+        <v>41.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.2</v>
+        <v>22.1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.0</v>
+        <v>12.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2036,7 +2006,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2068,7 +2038,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -2100,7 +2070,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -2132,7 +2102,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2164,7 +2134,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2196,7 +2166,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2228,7 +2198,7 @@
         <v>67</v>
       </c>
       <c r="J8" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -2260,7 +2230,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -2292,7 +2262,7 @@
         <v>67</v>
       </c>
       <c r="J10" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -2324,7 +2294,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
@@ -2356,7 +2326,7 @@
         <v>85</v>
       </c>
       <c r="J12" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -2388,7 +2358,7 @@
         <v>46</v>
       </c>
       <c r="J13" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -2420,7 +2390,7 @@
         <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
@@ -2452,7 +2422,7 @@
         <v>71</v>
       </c>
       <c r="J15" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
@@ -2484,7 +2454,7 @@
         <v>99</v>
       </c>
       <c r="J16" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -2516,7 +2486,7 @@
         <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -2524,28 +2494,28 @@
         <v>106</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
@@ -2553,77 +2523,77 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="J20" s="3">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>49</v>
@@ -2632,30 +2602,30 @@
         <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J21" s="3">
-        <v>65</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
@@ -2673,45 +2643,47 @@
         <v>129</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="G23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>134</v>
@@ -2720,7 +2692,7 @@
         <v>135</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>43</v>
@@ -2736,12 +2708,12 @@
         <v>137</v>
       </c>
       <c r="J24" s="3">
-        <v>88</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>138</v>
@@ -2763,24 +2735,24 @@
         <v>140</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="J25" s="3">
-        <v>5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>142</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>43</v>
@@ -2790,24 +2762,24 @@
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="J26" s="3">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>49</v>
@@ -2823,21 +2795,21 @@
         <v>146</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="J27" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>49</v>
@@ -2850,27 +2822,27 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J28" s="3">
-        <v>86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -2883,21 +2855,21 @@
         <v>153</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="J29" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>49</v>
@@ -2910,27 +2882,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J30" s="3">
-        <v>23</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -2940,27 +2912,27 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="J31" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -2973,24 +2945,24 @@
         <v>162</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="J32" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -3000,18 +2972,18 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>168</v>
@@ -3020,10 +2992,10 @@
         <v>169</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
@@ -3033,24 +3005,24 @@
         <v>170</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>43</v>
@@ -3063,27 +3035,27 @@
         <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>175</v>
+        <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
@@ -3093,24 +3065,24 @@
         <v>178</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>41</v>
+        <v>179</v>
       </c>
       <c r="J36" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>43</v>
@@ -3126,7 +3098,7 @@
         <v>183</v>
       </c>
       <c r="J37" s="3">
-        <v>67</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -3137,10 +3109,10 @@
         <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>43</v>
@@ -3153,51 +3125,51 @@
         <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="J38" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>112</v>
+        <v>188</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="J39" s="3">
-        <v>5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>142</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
@@ -3205,37 +3177,35 @@
       <c r="E40" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>189</v>
-      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>191</v>
+        <v>137</v>
       </c>
       <c r="J40" s="3">
-        <v>57</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>192</v>
+        <v>53</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
@@ -3245,10 +3215,10 @@
         <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="J41" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -3256,10 +3226,10 @@
         <v>106</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>197</v>
+        <v>139</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3272,27 +3242,27 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J42" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>53</v>
+        <v>198</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>49</v>
+        <v>201</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>38</v>
@@ -3302,24 +3272,24 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
@@ -3332,30 +3302,30 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="J44" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>112</v>
+        <v>201</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
@@ -3365,78 +3335,78 @@
         <v>206</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="J45" s="3">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="D46" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>41</v>
+        <v>213</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>139</v>
@@ -3445,64 +3415,64 @@
         <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>41</v>
+        <v>179</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>181</v>
+        <v>116</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>216</v>
+        <v>41</v>
       </c>
       <c r="J49" s="3">
-        <v>68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>53</v>
+        <v>198</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>49</v>
+        <v>201</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
@@ -3512,54 +3482,54 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>171</v>
+        <v>41</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>41</v>
+        <v>224</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>53</v>
+        <v>225</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3572,27 +3542,27 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>224</v>
+        <v>149</v>
       </c>
       <c r="J52" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>227</v>
+        <v>139</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>228</v>
+        <v>49</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>38</v>
@@ -3602,21 +3572,21 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>139</v>
@@ -3632,30 +3602,30 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="J54" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>235</v>
+        <v>139</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
@@ -3665,10 +3635,10 @@
         <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56">
@@ -3679,7 +3649,7 @@
         <v>238</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>235</v>
+        <v>139</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
@@ -3695,10 +3665,10 @@
         <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>199</v>
+        <v>41</v>
       </c>
       <c r="J56" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3679,10 @@
         <v>241</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>38</v>
@@ -3725,21 +3695,21 @@
         <v>242</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>53</v>
+        <v>243</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
@@ -3752,13 +3722,13 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>245</v>
+        <v>141</v>
       </c>
       <c r="J58" s="3">
-        <v>6</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59">
@@ -3769,70 +3739,70 @@
         <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J59" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>235</v>
+        <v>139</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="J60" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>53</v>
+        <v>253</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>135</v>
+        <v>255</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3842,54 +3812,54 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>245</v>
+        <v>149</v>
       </c>
       <c r="J61" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>255</v>
+        <v>110</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>135</v>
+        <v>258</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>137</v>
+        <v>224</v>
       </c>
       <c r="J62" s="3">
-        <v>88</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
@@ -3902,57 +3872,57 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="J63" s="3">
-        <v>88</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>261</v>
+        <v>53</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>169</v>
+        <v>268</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>38</v>
@@ -3962,57 +3932,57 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="J65" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>267</v>
+        <v>56</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>269</v>
+        <v>139</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>133</v>
+        <v>272</v>
       </c>
       <c r="J66" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>200</v>
+        <v>273</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>272</v>
+        <v>139</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>38</v>
@@ -4022,57 +3992,57 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>53</v>
+        <v>275</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>227</v>
+        <v>277</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>147</v>
+        <v>279</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>135</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>43</v>
@@ -4082,114 +4052,114 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>279</v>
+        <v>41</v>
       </c>
       <c r="J69" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>56</v>
+        <v>283</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>135</v>
+        <v>258</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>283</v>
+        <v>53</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>41</v>
+        <v>289</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>197</v>
+        <v>139</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>216</v>
+        <v>154</v>
       </c>
       <c r="J72" s="3">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>240</v>
+        <v>56</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
@@ -4202,34 +4172,32 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="J73" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>291</v>
+        <v>53</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>292</v>
+        <v>254</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>293</v>
+        <v>169</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>294</v>
-      </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
@@ -4237,10 +4205,10 @@
         <v>295</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="J74" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4254,97 +4222,99 @@
         <v>135</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>299</v>
+        <v>41</v>
       </c>
       <c r="J75" s="3">
-        <v>64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>300</v>
+        <v>53</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>301</v>
+        <v>168</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>235</v>
+        <v>139</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>245</v>
+        <v>41</v>
       </c>
       <c r="J76" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>168</v>
+        <v>247</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>169</v>
+        <v>302</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>112</v>
+        <v>188</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J77" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>305</v>
+        <v>110</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>306</v>
+        <v>145</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>43</v>
@@ -4354,325 +4324,263 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F79" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="G79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="D80" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="I81" s="3" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>34</v>
+        <v>315</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>319</v>
-      </c>
       <c r="I82" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>89</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>320</v>
+        <v>110</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>135</v>
+        <v>319</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>189</v>
-      </c>
+      <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="J83" s="3">
-        <v>88</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="D84" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>189</v>
-      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>171</v>
+        <v>289</v>
       </c>
       <c r="J84" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>327</v>
+        <v>247</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>131</v>
+        <v>248</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>328</v>
-      </c>
+      <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="I86" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J86" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J87" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="J88" s="3">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J88"/>
+  <autoFilter ref="A1:J86"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4759,8 +4667,6 @@
     <hyperlink ref="H84" r:id="rId83"/>
     <hyperlink ref="H85" r:id="rId84"/>
     <hyperlink ref="H86" r:id="rId85"/>
-    <hyperlink ref="H87" r:id="rId86"/>
-    <hyperlink ref="H88" r:id="rId87"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4768,9 +4674,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4802,13 +4708,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4816,113 +4722,113 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>55</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>58</v>
+        <v>266</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>59</v>
+        <v>267</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>268</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>62</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>106</v>
+        <v>243</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>107</v>
+        <v>273</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>109</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>122</v>
+        <v>293</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>129</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4930,296 +4836,11 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>331</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G23"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5228,21 +4849,6 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
-    <hyperlink ref="G23" r:id="rId22"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5256,23 +4862,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B3" s="3">
         <v>15</v>
@@ -5280,7 +4886,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>189</v>
+        <v>335</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -5288,15 +4894,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B6" s="3">
         <v>11</v>
@@ -5304,15 +4910,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
@@ -5320,15 +4926,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5336,7 +4942,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -5344,31 +4950,31 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5376,7 +4982,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5389,7 +4995,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5398,7 +5004,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2">
@@ -5427,7 +5033,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5435,7 +5041,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5459,7 +5065,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5467,7 +5073,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5475,7 +5081,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5483,7 +5089,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5491,7 +5097,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5499,15 +5105,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>220</v>
+        <v>59</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5515,7 +5121,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5529,23 +5135,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2">
@@ -5609,10 +5215,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C6" s="3">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5623,10 +5229,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="C7" s="3">
-        <v>5.0</v>
+        <v>5.3</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5637,13 +5243,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="C8" s="3">
-        <v>4.2</v>
+        <v>5.0</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5651,10 +5257,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>176</v>
       </c>
       <c r="C9" s="3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -5665,13 +5271,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="C10" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5679,13 +5285,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5693,13 +5299,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="C12" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5707,13 +5313,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="C13" s="3">
         <v>2.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5721,7 +5327,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5735,7 +5341,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5749,13 +5355,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>220</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.0</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5775,10 +5381,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2">
@@ -5797,10 +5403,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4">
@@ -5811,7 +5417,7 @@
         <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -5830,7 +5436,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2">
@@ -5838,15 +5444,15 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -5854,12 +5460,12 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5867,23 +5473,23 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>228</v>
+        <v>102</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5910,10 +5516,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5925,10 +5531,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5945,31 +5551,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3">
@@ -5977,31 +5583,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4">
@@ -6009,31 +5615,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>374</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5">
@@ -6041,31 +5647,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>252</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -6073,31 +5679,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7">
@@ -6114,13 +5720,13 @@
         <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="F7" s="3">
         <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>24</v>
@@ -6137,31 +5743,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>389</v>
+        <v>152</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="F8" s="3">
         <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -6169,31 +5775,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>392</v>
+        <v>280</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F9" s="3">
         <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>394</v>
+        <v>282</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>171</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -6201,31 +5807,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>312</v>
+        <v>386</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F10" s="3">
         <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>313</v>
+        <v>388</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -6242,13 +5848,13 @@
         <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="F11" s="3">
         <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>24</v>
@@ -6265,28 +5871,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F12" s="3">
         <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>85</v>
@@ -6297,31 +5903,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>402</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="F13" s="3">
+        <v>60</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="F13" s="3">
-        <v>76</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="14">
@@ -6329,31 +5935,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>35</v>
+        <v>254</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>36</v>
+        <v>255</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F14" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15">
@@ -6361,31 +5967,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>412</v>
+        <v>139</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F15" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16">
@@ -6393,31 +5999,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>200</v>
+        <v>407</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>272</v>
+        <v>408</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>369</v>
+        <v>409</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>224</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17">
@@ -6425,31 +6031,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>135</v>
+        <v>208</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>423</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -6457,31 +6063,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>424</v>
+        <v>321</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>426</v>
+        <v>145</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>427</v>
+        <v>362</v>
       </c>
       <c r="F18" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19">
@@ -6489,31 +6095,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>432</v>
+        <v>165</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>235</v>
+        <v>166</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F19" s="3">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>120</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6521,31 +6127,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>139</v>
+        <v>425</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F20" s="3">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>438</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21">
@@ -6553,31 +6159,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>439</v>
+        <v>406</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>177</v>
+        <v>428</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W33.xlsx
+++ b/reports/devops-jobs-israel-2026-W33.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="445">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-12T07:44:20</t>
+    <t xml:space="preserve">2026-08-13T07:46:05</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5%</t>
+    <t xml:space="preserve">2.5%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -423,84 +423,78 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
   </si>
   <si>
-    <t xml:space="preserve">Scytale</t>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4448083785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4448083785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4449509251</t>
   </si>
   <si>
@@ -534,6 +528,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4449541386</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">CodeValue</t>
   </si>
   <si>
@@ -546,765 +555,741 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4451527258</t>
   </si>
   <si>
-    <t xml:space="preserve">Mid-Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ArtAc</t>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Agentic Search)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid-senior-devops-engineer-at-artac-4449647364</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-agentic-search-at-nebius-4449552344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODDITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4452384011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGO NEXT Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4449550588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4449812270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4449562024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead (37248)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451509573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLVTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-tlvtech-4449569052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4449841507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4451528239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4450940462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4450225101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4449299724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solutions / Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APERIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/solutions-site-reliability-engineer-at-aperio-4451514889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alictus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-alictus-4450008323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-nimble-4452451963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4451564107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-07</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Agentic Search)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-agentic-search-at-nebius-4449552344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaos Engineer (Chaos DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/chaos-engineer-chaos-devops-at-check-point-software-4449688636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-artac-4449652341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLVTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-tlvtech-4449569052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4449841507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4449299724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4450225101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead (37248)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451509573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4451528239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4450940462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-voyantis-4448003083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solutions / Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APERIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/solutions-site-reliability-engineer-at-aperio-4451514889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4448004083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alictus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-alictus-4450008323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-nimble-4452451963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGO NEXT Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4451564107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-atera-4449731971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moonsite - Moonsoft Development Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-moonsite-moonsoft-development-ltd-4450448807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paytag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-cloud-engineer-at-paytag-4452727286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizon Technologies LTD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-horizon-technologies-ltd-4450148351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Client Oriented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-client-oriented-at-kpmg-israel-4451134408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-at-sqlink-group-4450469560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remedio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-remedio-4427566011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4452408106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGILINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-05</t>
   </si>
   <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-atera-4449731971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451456954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4449812270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4447388666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4449562024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Client Oriented</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-client-oriented-at-kpmg-israel-4451134408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4451336717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4449655270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4449550588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4447375577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4447391644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4452408106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGILINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
-  </si>
-  <si>
     <t xml:space="preserve">QuantHealth</t>
   </si>
   <si>
@@ -1323,19 +1308,19 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
@@ -1493,7 +1478,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
@@ -1501,7 +1486,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1509,7 +1494,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -1517,7 +1502,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1245</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="10">
@@ -1525,7 +1510,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1589,7 +1574,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -1616,20 +1601,20 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -1637,7 +1622,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1645,7 +1630,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1664,79 +1649,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>437</v>
+        <v>331</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>337</v>
+        <v>432</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B10" s="3">
         <v>17</v>
@@ -1744,15 +1729,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>439</v>
+        <v>327</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>335</v>
+        <v>434</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -1760,15 +1745,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
@@ -1776,15 +1761,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B16" s="3">
         <v>8</v>
@@ -1812,13 +1797,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2">
@@ -1829,10 +1814,10 @@
         <v>22</v>
       </c>
       <c r="C2" s="3">
-        <v>12.5</v>
+        <v>16.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1841,88 +1826,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3">
-        <v>38.0</v>
+        <v>34.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.0</v>
+        <v>1.9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>41.0</v>
+        <v>36.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>22.1</v>
+        <v>18.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>12.7</v>
+        <v>18.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1934,7 +1919,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2006,7 +1991,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2038,7 +2023,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -2070,7 +2055,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
@@ -2102,7 +2087,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2134,7 +2119,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2166,7 +2151,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2198,7 +2183,7 @@
         <v>67</v>
       </c>
       <c r="J8" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -2230,7 +2215,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -2262,7 +2247,7 @@
         <v>67</v>
       </c>
       <c r="J10" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -2294,7 +2279,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -2326,7 +2311,7 @@
         <v>85</v>
       </c>
       <c r="J12" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -2358,7 +2343,7 @@
         <v>46</v>
       </c>
       <c r="J13" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -2390,7 +2375,7 @@
         <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -2422,7 +2407,7 @@
         <v>71</v>
       </c>
       <c r="J15" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -2454,7 +2439,7 @@
         <v>99</v>
       </c>
       <c r="J16" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -2486,7 +2471,7 @@
         <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -2518,7 +2503,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2550,7 +2535,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2582,7 +2567,7 @@
         <v>119</v>
       </c>
       <c r="J20" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
@@ -2614,7 +2599,7 @@
         <v>124</v>
       </c>
       <c r="J21" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -2646,7 +2631,7 @@
         <v>130</v>
       </c>
       <c r="J22" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
@@ -2678,7 +2663,7 @@
         <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2692,7 +2677,7 @@
         <v>135</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>43</v>
@@ -2708,7 +2693,7 @@
         <v>137</v>
       </c>
       <c r="J24" s="3">
-        <v>6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25">
@@ -2719,7 +2704,7 @@
         <v>138</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>49</v>
@@ -2732,13 +2717,13 @@
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="J25" s="3">
-        <v>89</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2746,10 +2731,10 @@
         <v>110</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>49</v>
@@ -2762,13 +2747,13 @@
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -2779,7 +2764,7 @@
         <v>144</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>49</v>
@@ -2792,27 +2777,27 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="J27" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2822,27 +2807,27 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J28" s="3">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -2852,27 +2837,27 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J29" s="3">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>156</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
@@ -2882,13 +2867,13 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="J30" s="3">
-        <v>87</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2902,7 +2887,7 @@
         <v>135</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -2915,24 +2900,24 @@
         <v>160</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="J31" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -2942,27 +2927,27 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>163</v>
+        <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -2972,27 +2957,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="J33" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>37</v>
+        <v>171</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3002,13 +2987,13 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="J34" s="3">
-        <v>2</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35">
@@ -3016,13 +3001,13 @@
         <v>110</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>43</v>
@@ -3032,57 +3017,57 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J36" s="3">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>43</v>
@@ -3092,27 +3077,27 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="J37" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>43</v>
@@ -3122,54 +3107,56 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="J38" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>188</v>
+        <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="3"/>
+      <c r="F39" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J39" s="3">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
@@ -3182,54 +3169,54 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="J40" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>53</v>
+        <v>196</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="J41" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3242,27 +3229,27 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J42" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>198</v>
+        <v>53</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>201</v>
+        <v>49</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>38</v>
@@ -3272,70 +3259,70 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>131</v>
+        <v>206</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>201</v>
+        <v>116</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>149</v>
+        <v>41</v>
       </c>
       <c r="J45" s="3">
         <v>2</v>
@@ -3343,16 +3330,16 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>53</v>
+        <v>214</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>49</v>
+        <v>217</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>38</v>
@@ -3362,84 +3349,84 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>213</v>
+        <v>41</v>
       </c>
       <c r="J47" s="3">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>179</v>
+        <v>41</v>
       </c>
       <c r="J48" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>116</v>
@@ -3452,27 +3439,27 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
@@ -3482,57 +3469,57 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>208</v>
+        <v>141</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>224</v>
+        <v>109</v>
       </c>
       <c r="J51" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>49</v>
+        <v>217</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>38</v>
@@ -3542,10 +3529,10 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>149</v>
+        <v>41</v>
       </c>
       <c r="J52" s="3">
         <v>2</v>
@@ -3553,43 +3540,43 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>41</v>
+        <v>203</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
@@ -3602,54 +3589,54 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J54" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="J55" s="3">
-        <v>89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
@@ -3662,27 +3649,27 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>41</v>
+        <v>244</v>
       </c>
       <c r="J56" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>38</v>
@@ -3692,24 +3679,24 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="J57" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
@@ -3722,90 +3709,90 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J58" s="3">
-        <v>89</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="C59" s="3" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J59" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="J60" s="3">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>255</v>
+        <v>135</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
@@ -3815,7 +3802,7 @@
         <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>149</v>
+        <v>41</v>
       </c>
       <c r="J61" s="3">
         <v>2</v>
@@ -3823,19 +3810,19 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>110</v>
+        <v>257</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>258</v>
+        <v>184</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
@@ -3845,10 +3832,10 @@
         <v>259</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>224</v>
+        <v>161</v>
       </c>
       <c r="J62" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
@@ -3859,13 +3846,13 @@
         <v>261</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
@@ -3875,24 +3862,24 @@
         <v>262</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>263</v>
+        <v>188</v>
       </c>
       <c r="J63" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>53</v>
+        <v>263</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>38</v>
@@ -3905,10 +3892,10 @@
         <v>265</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J64" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -3919,40 +3906,40 @@
         <v>267</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>268</v>
+        <v>135</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="I65" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>56</v>
+        <v>270</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>139</v>
+        <v>272</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>38</v>
@@ -3962,24 +3949,24 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>272</v>
+        <v>109</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
@@ -3992,43 +3979,43 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>109</v>
+        <v>276</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="J68" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4039,7 +4026,7 @@
         <v>281</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>116</v>
@@ -4058,7 +4045,7 @@
         <v>41</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4069,7 +4056,7 @@
         <v>284</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
@@ -4088,48 +4075,48 @@
         <v>286</v>
       </c>
       <c r="J70" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>53</v>
+        <v>287</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J71" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
@@ -4142,13 +4129,13 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J72" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73">
@@ -4156,10 +4143,10 @@
         <v>56</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
@@ -4172,40 +4159,40 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>109</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>53</v>
+        <v>296</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="J74" s="3">
         <v>0</v>
@@ -4213,78 +4200,76 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>297</v>
+        <v>148</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>298</v>
-      </c>
+      <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>41</v>
+        <v>286</v>
       </c>
       <c r="J75" s="3">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>53</v>
+        <v>301</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>168</v>
+        <v>302</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>139</v>
+        <v>272</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="J76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>302</v>
+        <v>157</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>43</v>
@@ -4294,24 +4279,24 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="J77" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>110</v>
+        <v>307</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>49</v>
@@ -4319,61 +4304,63 @@
       <c r="E78" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>34</v>
+        <v>314</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>310</v>
+        <v>211</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>116</v>
@@ -4386,54 +4373,56 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>176</v>
+        <v>318</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>116</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F81" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="J81" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>49</v>
@@ -4441,146 +4430,22 @@
       <c r="E82" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>308</v>
-      </c>
+      <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>141</v>
+        <v>324</v>
       </c>
       <c r="J82" s="3">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="J84" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J85" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="J86" s="3">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J86"/>
+  <autoFilter ref="A1:J82"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4663,10 +4528,6 @@
     <hyperlink ref="H80" r:id="rId79"/>
     <hyperlink ref="H81" r:id="rId80"/>
     <hyperlink ref="H82" r:id="rId81"/>
-    <hyperlink ref="H83" r:id="rId82"/>
-    <hyperlink ref="H84" r:id="rId83"/>
-    <hyperlink ref="H85" r:id="rId84"/>
-    <hyperlink ref="H86" r:id="rId85"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4674,8 +4535,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4708,32 +4569,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>189</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>108</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4741,18 +4602,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>143</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>131</v>
+        <v>214</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4760,18 +4621,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4779,18 +4640,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4798,18 +4659,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>56</v>
+        <v>301</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>139</v>
+        <v>272</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4817,18 +4678,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>53</v>
+        <v>304</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>254</v>
+        <v>305</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4836,11 +4697,49 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>295</v>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -4849,6 +4748,8 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
+    <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4862,15 +4763,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B2" s="3">
         <v>16</v>
@@ -4878,7 +4779,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B3" s="3">
         <v>15</v>
@@ -4886,7 +4787,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -4894,15 +4795,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>308</v>
+        <v>190</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B6" s="3">
         <v>11</v>
@@ -4910,7 +4811,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B7" s="3">
         <v>11</v>
@@ -4918,7 +4819,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
@@ -4926,7 +4827,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B9" s="3">
         <v>10</v>
@@ -4934,7 +4835,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -4942,7 +4843,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -4950,7 +4851,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -4958,7 +4859,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -4966,7 +4867,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -4974,7 +4875,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -4982,10 +4883,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5004,7 +4905,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2">
@@ -5033,7 +4934,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5041,15 +4942,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5057,7 +4958,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5065,7 +4966,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5073,7 +4974,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5081,7 +4982,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5089,7 +4990,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5097,7 +4998,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5142,16 +5043,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2">
@@ -5257,10 +5158,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="C9" s="3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -5271,13 +5172,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>247</v>
+        <v>111</v>
       </c>
       <c r="C10" s="3">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5285,13 +5186,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5299,7 +5200,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5327,7 +5228,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5341,7 +5242,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5381,10 +5282,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2">
@@ -5392,7 +5293,7 @@
         <v>82</v>
       </c>
       <c r="B2" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5403,10 +5304,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4">
@@ -5414,10 +5315,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5436,7 +5337,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2">
@@ -5444,7 +5345,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -5452,20 +5353,20 @@
         <v>116</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>217</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5481,7 +5382,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5489,7 +5390,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5504,7 +5405,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5516,10 +5417,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5531,10 +5432,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5557,16 +5458,16 @@
         <v>284</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
@@ -5575,7 +5476,7 @@
         <v>285</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3">
@@ -5583,31 +5484,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4">
@@ -5615,31 +5516,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>367</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5">
@@ -5647,28 +5548,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>41</v>
@@ -5682,25 +5583,25 @@
         <v>280</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>119</v>
@@ -5720,13 +5621,13 @@
         <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="F7" s="3">
         <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>24</v>
@@ -5743,31 +5644,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="F8" s="3">
         <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -5781,16 +5682,16 @@
         <v>281</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F9" s="3">
         <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
@@ -5807,31 +5708,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>385</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>386</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F10" s="3">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>388</v>
+        <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>179</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -5839,31 +5740,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>379</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>380</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="F11" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>45</v>
+        <v>382</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -5871,31 +5772,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>391</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>139</v>
+        <v>36</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>85</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13">
@@ -5903,31 +5804,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>387</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>197</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14">
@@ -5935,31 +5836,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F14" s="3">
+        <v>51</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="F14" s="3">
-        <v>52</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="15">
@@ -5967,31 +5868,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="F15" s="3">
+        <v>48</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="F15" s="3">
-        <v>52</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>404</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>405</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16">
@@ -5999,31 +5900,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>408</v>
+        <v>208</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>409</v>
+        <v>355</v>
       </c>
       <c r="F16" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>412</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17">
@@ -6031,31 +5932,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>208</v>
+        <v>141</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F17" s="3">
         <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18">
@@ -6063,31 +5964,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>321</v>
+        <v>410</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>417</v>
+        <v>163</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F18" s="3">
         <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>420</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -6095,31 +5996,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>165</v>
+        <v>414</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>166</v>
+        <v>233</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="F19" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>41</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20">
@@ -6127,31 +6028,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>321</v>
+        <v>402</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F20" s="3">
         <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>289</v>
+        <v>422</v>
       </c>
     </row>
     <row r="21">
@@ -6159,31 +6060,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="F21" s="3">
         <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W33.xlsx
+++ b/reports/devops-jobs-israel-2026-W33.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="443">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-13T07:46:05</t>
+    <t xml:space="preserve">2026-08-14T07:44:04</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -381,12 +381,24 @@
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Ansible, Docker, CI/CD, Linux, Python, Bash/Shell, Prometheus, Grafana, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7818899003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
   </si>
   <si>
@@ -423,796 +435,826 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
   </si>
   <si>
-    <t xml:space="preserve">Connecteam</t>
+    <t xml:space="preserve">Fiverr</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
   </si>
   <si>
-    <t xml:space="preserve">Buildots</t>
+    <t xml:space="preserve">Agora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4452939013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4449509251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4449541386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4451527258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Agentic Search)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-agentic-search-at-nebius-4449552344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODDITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4452384011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4448083785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4449509251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4449550588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonkean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4452977126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4449812270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4449562024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLVTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-tlvtech-4449569052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4449841507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4451528239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moonsite - Moonsoft Development Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-moonsite-moonsoft-development-ltd-4450448807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solutions / Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APERIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/solutions-site-reliability-engineer-at-aperio-4451514889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-peax-dorcom-4450484648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-comblack-4451546691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4449541386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4451527258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Agentic Search)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-agentic-search-at-nebius-4449552344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODDITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4452384011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGO NEXT Insurance</t>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453261687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-nimble-4452451963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-ai-4450816877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paytag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-cloud-engineer-at-paytag-4452727286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizon Technologies LTD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-horizon-technologies-ltd-4450494623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Client Oriented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-client-oriented-at-kpmg-israel-4451134408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-at-sqlink-group-4450469560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semperis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-semperis-4438770193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4450457986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-comblack-4454021597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remedio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-remedio-4427566011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4452408106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4451564107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
   </si>
   <si>
     <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4449550588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4449812270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4449562024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead (37248)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4451509573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLVTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-tlvtech-4449569052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4449841507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4451528239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4450940462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4450225101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4449299724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solutions / Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APERIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/solutions-site-reliability-engineer-at-aperio-4451514889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alictus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-alictus-4450008323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-nimble-4452451963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4451564107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-atera-4449731971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moonsite - Moonsoft Development Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-moonsite-moonsoft-development-ltd-4450448807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paytag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-cloud-engineer-at-paytag-4452727286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizon Technologies LTD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-horizon-technologies-ltd-4450148351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Client Oriented</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-client-oriented-at-kpmg-israel-4451134408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-at-sqlink-group-4450469560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remedio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-remedio-4427566011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4452408106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
   </si>
   <si>
     <t xml:space="preserve">IT Operations Engineer I</t>
@@ -1225,54 +1267,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
     <t xml:space="preserve">AGILINA</t>
@@ -1486,7 +1480,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1494,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1502,7 +1496,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1158</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="10">
@@ -1574,7 +1568,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -1582,7 +1576,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1601,20 +1595,20 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -1622,7 +1616,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1630,7 +1624,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1649,18 +1643,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -1668,60 +1662,60 @@
         <v>336</v>
       </c>
       <c r="B3" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B10" s="3">
         <v>17</v>
@@ -1732,23 +1726,23 @@
         <v>327</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>434</v>
+        <v>326</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>329</v>
+        <v>432</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -1761,18 +1755,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B15" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1797,13 +1791,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="2">
@@ -1811,13 +1805,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3">
-        <v>16.9</v>
+        <v>13.6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1829,85 +1823,85 @@
         <v>64</v>
       </c>
       <c r="C3" s="3">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>36.7</v>
+        <v>37.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.3</v>
+        <v>19.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>18.3</v>
+        <v>19.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1991,7 +1985,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2023,7 +2017,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -2055,7 +2049,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -2087,7 +2081,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2119,7 +2113,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2151,7 +2145,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -2183,7 +2177,7 @@
         <v>67</v>
       </c>
       <c r="J8" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -2215,7 +2209,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -2247,7 +2241,7 @@
         <v>67</v>
       </c>
       <c r="J10" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
@@ -2279,7 +2273,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -2311,7 +2305,7 @@
         <v>85</v>
       </c>
       <c r="J12" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -2343,7 +2337,7 @@
         <v>46</v>
       </c>
       <c r="J13" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -2375,7 +2369,7 @@
         <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -2407,7 +2401,7 @@
         <v>71</v>
       </c>
       <c r="J15" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -2439,7 +2433,7 @@
         <v>99</v>
       </c>
       <c r="J16" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17">
@@ -2471,7 +2465,7 @@
         <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -2503,7 +2497,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2535,7 +2529,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2567,7 +2561,7 @@
         <v>119</v>
       </c>
       <c r="J20" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21">
@@ -2599,7 +2593,7 @@
         <v>124</v>
       </c>
       <c r="J21" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -2607,10 +2601,10 @@
         <v>125</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
@@ -2619,30 +2613,30 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J22" s="3">
-        <v>67</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>49</v>
@@ -2660,40 +2654,42 @@
         <v>133</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="J23" s="3">
-        <v>2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="G24" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>90</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -2704,7 +2700,7 @@
         <v>138</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>49</v>
@@ -2717,13 +2713,13 @@
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>109</v>
       </c>
       <c r="J25" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2731,10 +2727,10 @@
         <v>110</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>49</v>
@@ -2753,21 +2749,21 @@
         <v>143</v>
       </c>
       <c r="J26" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>43</v>
@@ -2777,27 +2773,27 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J27" s="3">
-        <v>3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2813,7 +2809,7 @@
         <v>151</v>
       </c>
       <c r="J28" s="3">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2824,7 +2820,7 @@
         <v>153</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>49</v>
@@ -2843,7 +2839,7 @@
         <v>155</v>
       </c>
       <c r="J29" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30">
@@ -2870,24 +2866,24 @@
         <v>158</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J30" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -2897,18 +2893,18 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>161</v>
+        <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>163</v>
@@ -2917,7 +2913,7 @@
         <v>164</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -2930,24 +2926,24 @@
         <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="J32" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>167</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -2957,27 +2953,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="J33" s="3">
-        <v>3</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -2987,27 +2983,27 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>173</v>
+        <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>86</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>176</v>
+        <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>43</v>
@@ -3020,24 +3016,24 @@
         <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>43</v>
@@ -3047,27 +3043,27 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>181</v>
+        <v>41</v>
       </c>
       <c r="J36" s="3">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>182</v>
+        <v>106</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>43</v>
@@ -3077,24 +3073,24 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J37" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>186</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>49</v>
@@ -3102,29 +3098,31 @@
       <c r="E38" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J38" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>49</v>
@@ -3132,31 +3130,29 @@
       <c r="E39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>190</v>
-      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
@@ -3172,40 +3168,40 @@
         <v>195</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>196</v>
+        <v>53</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>197</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>199</v>
+        <v>41</v>
       </c>
       <c r="J41" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -3219,7 +3215,7 @@
         <v>201</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>43</v>
@@ -3232,10 +3228,10 @@
         <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>203</v>
+        <v>41</v>
       </c>
       <c r="J42" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -3243,10 +3239,10 @@
         <v>53</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
@@ -3259,30 +3255,30 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
@@ -3292,84 +3288,84 @@
         <v>209</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="J44" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>211</v>
+        <v>163</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>212</v>
+        <v>139</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>217</v>
+        <v>49</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>53</v>
+        <v>205</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>208</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>38</v>
@@ -3379,40 +3375,40 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J47" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="J48" s="3">
         <v>2</v>
@@ -3420,16 +3416,16 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>116</v>
+        <v>208</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>38</v>
@@ -3439,87 +3435,87 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>217</v>
+        <v>116</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>131</v>
+        <v>222</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>217</v>
+        <v>49</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>38</v>
@@ -3529,87 +3525,87 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="J52" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>233</v>
+        <v>139</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>203</v>
+        <v>41</v>
       </c>
       <c r="J53" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>146</v>
+        <v>235</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>49</v>
+        <v>208</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
@@ -3619,73 +3615,75 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="J55" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>233</v>
+        <v>157</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>244</v>
+        <v>41</v>
       </c>
       <c r="J56" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>216</v>
+        <v>139</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>217</v>
+        <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3693,10 +3691,10 @@
         <v>53</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
@@ -3709,27 +3707,27 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J58" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>53</v>
+        <v>248</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>217</v>
+        <v>116</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>38</v>
@@ -3739,54 +3737,54 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J59" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="J60" s="3">
-        <v>90</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
@@ -3799,24 +3797,24 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>116</v>
@@ -3829,117 +3827,117 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>161</v>
+        <v>261</v>
       </c>
       <c r="J62" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>188</v>
+        <v>265</v>
       </c>
       <c r="J63" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>204</v>
+        <v>267</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>264</v>
+        <v>194</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>146</v>
+        <v>269</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>135</v>
+        <v>272</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>49</v>
+        <v>273</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>269</v>
+        <v>151</v>
       </c>
       <c r="J65" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>271</v>
+        <v>197</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>272</v>
+        <v>164</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>38</v>
@@ -3949,57 +3947,57 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>56</v>
+        <v>277</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>276</v>
+        <v>151</v>
       </c>
       <c r="J67" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>135</v>
+        <v>281</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>38</v>
@@ -4009,40 +4007,40 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>109</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="J69" s="3">
         <v>2</v>
@@ -4050,19 +4048,19 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>284</v>
+        <v>163</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
@@ -4072,24 +4070,24 @@
         <v>285</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>286</v>
+        <v>151</v>
       </c>
       <c r="J70" s="3">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="C71" s="3" t="s">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>116</v>
+        <v>273</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>43</v>
@@ -4099,24 +4097,24 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="I71" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="I71" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="J71" s="3">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>292</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
@@ -4129,27 +4127,27 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J72" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>56</v>
+        <v>293</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="D73" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>38</v>
@@ -4162,10 +4160,10 @@
         <v>295</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -4176,7 +4174,7 @@
         <v>297</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>184</v>
+        <v>281</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>116</v>
@@ -4192,10 +4190,10 @@
         <v>298</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4203,56 +4201,58 @@
         <v>299</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>148</v>
+        <v>300</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>171</v>
+        <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F75" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>286</v>
+        <v>189</v>
       </c>
       <c r="J75" s="3">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>301</v>
+        <v>34</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>116</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="J76" s="3">
         <v>0</v>
@@ -4260,75 +4260,75 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>308</v>
+        <v>200</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>190</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>49</v>
@@ -4337,7 +4337,7 @@
         <v>38</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>312</v>
+        <v>187</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>23</v>
@@ -4346,7 +4346,7 @@
         <v>313</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="J79" s="3">
         <v>0</v>
@@ -4357,26 +4357,26 @@
         <v>314</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>211</v>
+        <v>315</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>116</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="J80" s="3">
         <v>0</v>
@@ -4384,10 +4384,10 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>318</v>
+        <v>249</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>157</v>
@@ -4398,31 +4398,29 @@
       <c r="E81" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="3"/>
+      <c r="G81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="I81" s="3" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="J81" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>322</v>
-      </c>
       <c r="C82" s="3" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>49</v>
@@ -4435,13 +4433,13 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="I82" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="I82" s="3" t="s">
-        <v>324</v>
-      </c>
       <c r="J82" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -4535,8 +4533,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4569,13 +4567,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4583,18 +4581,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>193</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4602,18 +4600,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4621,18 +4619,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>245</v>
+        <v>53</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>246</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4645,13 +4643,13 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>296</v>
+        <v>248</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>184</v>
+        <v>250</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4659,18 +4657,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>272</v>
+        <v>139</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4678,18 +4676,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>303</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4697,18 +4695,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>306</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>310</v>
+        <v>275</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>311</v>
+        <v>197</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4716,18 +4714,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>313</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>314</v>
+        <v>277</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>315</v>
+        <v>157</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4735,11 +4733,106 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>316</v>
       </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>319</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G15"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -4750,6 +4843,11 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4763,79 +4861,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>329</v>
+        <v>187</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>190</v>
+        <v>328</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B6" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -4843,15 +4941,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -4859,7 +4957,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -4867,7 +4965,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -4875,7 +4973,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -4883,7 +4981,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -4905,7 +5003,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2">
@@ -4934,7 +5032,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -4942,23 +5040,23 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>197</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -4966,7 +5064,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -4974,7 +5072,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -4982,7 +5080,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -4990,7 +5088,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>211</v>
+        <v>130</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -4998,7 +5096,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>246</v>
+        <v>145</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5006,15 +5104,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5022,7 +5120,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5043,16 +5141,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2">
@@ -5116,10 +5214,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C6" s="3">
-        <v>5.8</v>
+        <v>6.0</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5130,10 +5228,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C7" s="3">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5144,10 +5242,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="C8" s="3">
-        <v>5.0</v>
+        <v>5.3</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -5158,13 +5256,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="C9" s="3">
-        <v>3.6</v>
+        <v>5.0</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5172,13 +5270,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="C10" s="3">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5186,13 +5284,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5200,13 +5298,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -5214,10 +5312,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -5228,10 +5326,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -5242,7 +5340,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>246</v>
+        <v>145</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5282,10 +5380,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="2">
@@ -5304,10 +5402,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4">
@@ -5315,10 +5413,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -5337,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2">
@@ -5345,7 +5443,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -5358,18 +5456,18 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>217</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>208</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -5382,7 +5480,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>171</v>
+        <v>273</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5390,9 +5488,17 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5417,10 +5523,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5432,10 +5538,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5452,31 +5558,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="3">
@@ -5484,31 +5590,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="4">
@@ -5516,31 +5622,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="5">
@@ -5548,28 +5654,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>41</v>
@@ -5580,28 +5686,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>119</v>
@@ -5621,13 +5727,13 @@
         <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F7" s="3">
         <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>24</v>
@@ -5644,31 +5750,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F8" s="3">
         <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5676,28 +5782,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>157</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F9" s="3">
         <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>282</v>
+        <v>376</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>41</v>
@@ -5717,13 +5823,13 @@
         <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F10" s="3">
         <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>24</v>
@@ -5740,19 +5846,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>355</v>
-      </c>
       <c r="F11" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>381</v>
@@ -5764,7 +5870,7 @@
         <v>382</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>85</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -5775,28 +5881,28 @@
         <v>383</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>384</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F12" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -5804,31 +5910,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>387</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F13" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>388</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>389</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>390</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14">
@@ -5836,31 +5942,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F14" s="3">
+        <v>52</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>394</v>
-      </c>
-      <c r="F14" s="3">
-        <v>51</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="15">
@@ -5868,31 +5974,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="F15" s="3">
+        <v>51</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F15" s="3">
-        <v>48</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="16">
@@ -5900,28 +6006,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F16" s="3">
         <v>48</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>404</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>405</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>109</v>
@@ -5932,31 +6038,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>402</v>
+        <v>314</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F17" s="3">
         <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="18">
@@ -5964,28 +6070,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F18" s="3">
         <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>41</v>
@@ -5996,31 +6102,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F19" s="3">
+        <v>48</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="F19" s="3">
-        <v>47</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>416</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>417</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
@@ -6028,31 +6134,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>402</v>
+        <v>314</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F20" s="3">
         <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="21">
@@ -6060,31 +6166,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="F21" s="3">
         <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>426</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W33.xlsx
+++ b/reports/devops-jobs-israel-2026-W33.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="450">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-14T07:44:04</t>
+    <t xml:space="preserve">2026-08-16T06:53:08</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5%</t>
+    <t xml:space="preserve">1.2%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -435,6 +435,18 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
   </si>
   <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4443370175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fiverr</t>
   </si>
   <si>
@@ -468,72 +480,75 @@
     <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4452939013</t>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4449509251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4449541386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451456954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonkean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4452977126</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4449509251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4449541386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
     <t xml:space="preserve">CodeValue</t>
   </si>
   <si>
@@ -546,6 +561,213 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4451527258</t>
   </si>
   <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLVTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-tlvtech-4449569052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4449841507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4449550588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4449812270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4449562024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4451528239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moonsite - Moonsoft Development Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-moonsite-moonsoft-development-ltd-4450448807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solutions / Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APERIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/solutions-site-reliability-engineer-at-aperio-4451514889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Production Engineer</t>
   </si>
   <si>
@@ -558,25 +780,151 @@
     <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer (Agentic Search)</t>
   </si>
   <si>
     <t xml:space="preserve">Nebius</t>
   </si>
   <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-agentic-search-at-nebius-4449552344</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-nimble-4452451963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-ai-4450816877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
     <t xml:space="preserve">Silverfort</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-22</t>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
   </si>
   <si>
     <t xml:space="preserve">ODDITY</t>
@@ -588,235 +936,163 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4452384011</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4449550588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonkean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4452977126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4449812270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4449562024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLVTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-tlvtech-4449569052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4449841507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4451528239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moonsite - Moonsoft Development Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-moonsite-moonsoft-development-ltd-4450448807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solutions / Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APERIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/solutions-site-reliability-engineer-at-aperio-4451514889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-peax-dorcom-4450484648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
+    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizon Technologies LTD.</t>
   </si>
   <si>
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-comblack-4451546691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-horizon-technologies-ltd-4450494623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Client Oriented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-client-oriented-at-kpmg-israel-4451134408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-at-sqlink-group-4450469560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4450457986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-comblack-4454021597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remedio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-remedio-4427566011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
@@ -825,276 +1101,36 @@
     <t xml:space="preserve">Helfy</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453261687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-nimble-4452451963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-ai-4450816877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paytag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-cloud-engineer-at-paytag-4452727286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizon Technologies LTD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-horizon-technologies-ltd-4450494623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Client Oriented</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-client-oriented-at-kpmg-israel-4451134408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-at-sqlink-group-4450469560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semperis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-semperis-4438770193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4450457986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-comblack-4454021597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remedio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-remedio-4427566011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
+    <t xml:space="preserve">software development student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-development-student-at-radware-4452112960</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calanit by one</t>
   </si>
   <si>
@@ -1128,9 +1164,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
   </si>
   <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1149,9 +1182,6 @@
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4451564107</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1182,6 +1212,54 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
   </si>
   <si>
+    <t xml:space="preserve">MER Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-mer-group-4436525380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlainID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-plainid-4451417266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenzai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-tenzai-4448410816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
   </si>
   <si>
@@ -1191,6 +1269,24 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
   </si>
   <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator &amp; IT</t>
   </si>
   <si>
@@ -1206,9 +1302,6 @@
     <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
     <t xml:space="preserve">etoro</t>
   </si>
   <si>
@@ -1224,78 +1317,6 @@
     <t xml:space="preserve">2026-07-01</t>
   </si>
   <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGILINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1305,13 +1326,13 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
@@ -1472,7 +1493,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -1480,7 +1501,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1488,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -1496,7 +1517,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1172</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="10">
@@ -1504,7 +1525,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1568,7 +1589,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -1595,36 +1616,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1643,130 +1664,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B2" s="3">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>332</v>
+        <v>434</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>427</v>
+        <v>338</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>330</v>
+        <v>437</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>430</v>
+        <v>336</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>431</v>
+        <v>341</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>432</v>
+        <v>332</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>335</v>
+        <v>439</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1791,13 +1812,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2">
@@ -1808,10 +1829,10 @@
         <v>23</v>
       </c>
       <c r="C2" s="3">
-        <v>13.6</v>
+        <v>11.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1823,85 +1844,85 @@
         <v>64</v>
       </c>
       <c r="C3" s="3">
-        <v>34.4</v>
+        <v>34.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.6</v>
+        <v>8.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>37.0</v>
+        <v>32.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.2</v>
+        <v>17.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>19.0</v>
+        <v>15.8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1985,7 +2006,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2017,7 +2038,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -2049,7 +2070,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
@@ -2081,7 +2102,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2113,7 +2134,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -2145,7 +2166,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2177,7 +2198,7 @@
         <v>67</v>
       </c>
       <c r="J8" s="3">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
@@ -2209,7 +2230,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -2241,7 +2262,7 @@
         <v>67</v>
       </c>
       <c r="J10" s="3">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -2273,7 +2294,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -2305,7 +2326,7 @@
         <v>85</v>
       </c>
       <c r="J12" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -2337,7 +2358,7 @@
         <v>46</v>
       </c>
       <c r="J13" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -2369,7 +2390,7 @@
         <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -2401,7 +2422,7 @@
         <v>71</v>
       </c>
       <c r="J15" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -2433,7 +2454,7 @@
         <v>99</v>
       </c>
       <c r="J16" s="3">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -2465,7 +2486,7 @@
         <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
@@ -2497,7 +2518,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2529,7 +2550,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2561,7 +2582,7 @@
         <v>119</v>
       </c>
       <c r="J20" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
@@ -2593,7 +2614,7 @@
         <v>124</v>
       </c>
       <c r="J21" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -2625,7 +2646,7 @@
         <v>128</v>
       </c>
       <c r="J22" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -2657,7 +2678,7 @@
         <v>134</v>
       </c>
       <c r="J23" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24">
@@ -2689,7 +2710,7 @@
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -2703,7 +2724,7 @@
         <v>139</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>43</v>
@@ -2716,10 +2737,10 @@
         <v>140</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="J25" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -2727,10 +2748,10 @@
         <v>110</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>49</v>
@@ -2743,10 +2764,10 @@
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="J26" s="3">
         <v>4</v>
@@ -2754,16 +2775,16 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>145</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>43</v>
@@ -2773,27 +2794,27 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="J27" s="3">
-        <v>67</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>149</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2803,27 +2824,27 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J28" s="3">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>153</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -2833,24 +2854,24 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="J29" s="3">
-        <v>89</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>116</v>
@@ -2863,27 +2884,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>143</v>
+        <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -2893,27 +2914,27 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="J31" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -2926,114 +2947,114 @@
         <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="J32" s="3">
-        <v>4</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>168</v>
+        <v>49</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="J33" s="3">
-        <v>87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>173</v>
+        <v>37</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="J34" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>175</v>
+        <v>53</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J35" s="3">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>43</v>
@@ -3043,24 +3064,24 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>49</v>
@@ -3073,62 +3094,60 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J37" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="J38" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
@@ -3138,54 +3157,54 @@
         <v>192</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>189</v>
+        <v>41</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>193</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="J40" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>53</v>
+        <v>188</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>38</v>
@@ -3195,10 +3214,10 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>41</v>
+        <v>197</v>
       </c>
       <c r="J41" s="3">
         <v>3</v>
@@ -3209,10 +3228,10 @@
         <v>110</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>116</v>
@@ -3225,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J42" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -3239,10 +3258,10 @@
         <v>53</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>203</v>
+        <v>160</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
@@ -3255,43 +3274,43 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>205</v>
+        <v>110</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>208</v>
+        <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>189</v>
+        <v>41</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -3299,10 +3318,10 @@
         <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
@@ -3315,70 +3334,70 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>41</v>
+        <v>206</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>41</v>
+        <v>197</v>
       </c>
       <c r="J47" s="3">
         <v>3</v>
@@ -3386,19 +3405,19 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>135</v>
+        <v>213</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
@@ -3408,24 +3427,24 @@
         <v>216</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>208</v>
+        <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>38</v>
@@ -3435,54 +3454,54 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="J49" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>189</v>
+        <v>41</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>224</v>
+        <v>143</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>49</v>
@@ -3498,54 +3517,54 @@
         <v>225</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="J51" s="3">
-        <v>25</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>151</v>
+        <v>230</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>38</v>
@@ -3555,10 +3574,10 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>41</v>
+        <v>197</v>
       </c>
       <c r="J53" s="3">
         <v>3</v>
@@ -3566,16 +3585,16 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>43</v>
@@ -3585,149 +3604,149 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="J54" s="3">
-        <v>22</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>207</v>
+        <v>154</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F55" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>189</v>
+        <v>41</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>241</v>
-      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>41</v>
+        <v>248</v>
       </c>
       <c r="J57" s="3">
-        <v>3</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>53</v>
+        <v>249</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>116</v>
+        <v>256</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>38</v>
@@ -3737,24 +3756,24 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>151</v>
+        <v>258</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3767,234 +3786,234 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="J60" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>256</v>
+        <v>170</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>139</v>
+        <v>263</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="J62" s="3">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>139</v>
+        <v>255</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>49</v>
+        <v>256</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>265</v>
+        <v>175</v>
       </c>
       <c r="J63" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>269</v>
+        <v>41</v>
       </c>
       <c r="J64" s="3">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>272</v>
+        <v>154</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>273</v>
+        <v>116</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>197</v>
+        <v>278</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>151</v>
+        <v>280</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>277</v>
+        <v>53</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>151</v>
+        <v>283</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>116</v>
@@ -4007,24 +4026,24 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>109</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
@@ -4037,24 +4056,24 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>109</v>
       </c>
       <c r="J69" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
@@ -4067,57 +4086,57 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>151</v>
+        <v>238</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>287</v>
+        <v>160</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>272</v>
+        <v>143</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>273</v>
+        <v>49</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>289</v>
+        <v>175</v>
       </c>
       <c r="J71" s="3">
-        <v>85</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>139</v>
+        <v>255</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>49</v>
+        <v>256</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>43</v>
@@ -4127,57 +4146,57 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>148</v>
+        <v>248</v>
       </c>
       <c r="J72" s="3">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>294</v>
+        <v>143</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>297</v>
+        <v>149</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>281</v>
+        <v>163</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>43</v>
@@ -4187,72 +4206,72 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="J74" s="3">
-        <v>1</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>299</v>
+        <v>47</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="J75" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>34</v>
+        <v>305</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>250</v>
+        <v>143</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="J76" s="3">
         <v>0</v>
@@ -4260,137 +4279,135 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>305</v>
+        <v>34</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>139</v>
+        <v>309</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>187</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="J77" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>200</v>
+        <v>312</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>309</v>
+        <v>143</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F78" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>189</v>
+        <v>41</v>
       </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>312</v>
+        <v>198</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>139</v>
+        <v>315</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>187</v>
-      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>314</v>
+        <v>188</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>316</v>
+        <v>143</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>151</v>
+        <v>319</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>249</v>
+        <v>321</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>157</v>
+        <v>322</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>116</v>
@@ -4403,27 +4420,27 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>321</v>
+        <v>275</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>198</v>
+        <v>154</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>43</v>
@@ -4433,17 +4450,47 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>323</v>
+        <v>175</v>
       </c>
       <c r="J82" s="3">
-        <v>31</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="J83" s="3">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J82"/>
+  <autoFilter ref="A1:J83"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4526,6 +4573,7 @@
     <hyperlink ref="H80" r:id="rId79"/>
     <hyperlink ref="H81" r:id="rId80"/>
     <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4533,8 +4581,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4567,13 +4615,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4581,18 +4629,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>305</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4600,254 +4648,14 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
-    <hyperlink ref="G4" r:id="rId3"/>
-    <hyperlink ref="G5" r:id="rId4"/>
-    <hyperlink ref="G6" r:id="rId5"/>
-    <hyperlink ref="G7" r:id="rId6"/>
-    <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4861,15 +4669,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B2" s="3">
         <v>17</v>
@@ -4877,7 +4685,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -4885,15 +4693,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>334</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="B5" s="3">
         <v>15</v>
@@ -4901,7 +4709,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B6" s="3">
         <v>12</v>
@@ -4909,7 +4717,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
@@ -4917,7 +4725,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
@@ -4925,7 +4733,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
@@ -4933,7 +4741,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -4941,7 +4749,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -4949,7 +4757,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -4957,7 +4765,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -4965,7 +4773,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -4973,7 +4781,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>301</v>
+        <v>344</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -4981,10 +4789,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5003,7 +4811,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2">
@@ -5032,7 +4840,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5040,7 +4848,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5048,7 +4856,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5096,7 +4904,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5104,7 +4912,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5141,16 +4949,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2">
@@ -5270,7 +5078,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C10" s="3">
         <v>4.2</v>
@@ -5284,10 +5092,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>249</v>
+        <v>149</v>
       </c>
       <c r="C11" s="3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -5298,7 +5106,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="C12" s="3">
         <v>3.6</v>
@@ -5326,7 +5134,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -5340,7 +5148,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>145</v>
+        <v>275</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5380,10 +5188,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2">
@@ -5391,7 +5199,7 @@
         <v>82</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5405,7 +5213,7 @@
         <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4">
@@ -5413,10 +5221,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -5435,7 +5243,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2">
@@ -5451,7 +5259,7 @@
         <v>116</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -5459,12 +5267,12 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -5472,15 +5280,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>273</v>
+        <v>102</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5488,15 +5296,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5511,7 +5319,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5523,10 +5331,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5538,10 +5346,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5558,31 +5366,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>266</v>
+        <v>120</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>267</v>
+        <v>121</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>268</v>
+        <v>123</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>351</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3">
@@ -5590,31 +5398,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4">
@@ -5622,31 +5430,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>250</v>
+        <v>143</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>361</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5">
@@ -5654,31 +5462,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>198</v>
+        <v>309</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>41</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6">
@@ -5686,31 +5494,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>277</v>
+        <v>374</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -5718,31 +5526,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>378</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="F7" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8">
@@ -5750,31 +5558,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>371</v>
+        <v>81</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>372</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F8" s="3">
         <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>361</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -5782,31 +5590,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>277</v>
+        <v>382</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>249</v>
+        <v>383</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="F9" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>41</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -5814,31 +5622,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>274</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>275</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>36</v>
+        <v>154</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="F10" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>45</v>
+        <v>276</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -5846,31 +5654,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>378</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>379</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="F11" s="3">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>382</v>
+        <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>185</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -5878,31 +5686,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -5910,31 +5718,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>394</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>185</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
@@ -5942,31 +5750,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>139</v>
+        <v>398</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15">
@@ -5974,31 +5782,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>397</v>
+        <v>173</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F15" s="3">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>400</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
@@ -6006,31 +5814,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>314</v>
+        <v>402</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>402</v>
+        <v>173</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="F16" s="3">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17">
@@ -6038,31 +5846,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>314</v>
+        <v>409</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="F17" s="3">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>408</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -6070,31 +5878,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>161</v>
+        <v>36</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F18" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19">
@@ -6102,31 +5910,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>224</v>
+        <v>418</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F19" s="3">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>128</v>
+        <v>421</v>
       </c>
     </row>
     <row r="20">
@@ -6134,31 +5942,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>314</v>
+        <v>422</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>417</v>
+        <v>143</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F20" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21">
@@ -6166,31 +5974,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>198</v>
+        <v>428</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
